--- a/KBL-Business flow/target/Data/Kbl datas.xlsx
+++ b/KBL-Business flow/target/Data/Kbl datas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>S.NO-0</t>
   </si>
@@ -47,6 +47,33 @@
   </si>
   <si>
     <t>D11130080576</t>
+  </si>
+  <si>
+    <t>kbl@123</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Ready To Ship</t>
+  </si>
+  <si>
+    <t>CND699580044</t>
+  </si>
+  <si>
+    <t>dattatray.jadhav@kbl.co.in</t>
+  </si>
+  <si>
+    <t>KBLSTAGE77154</t>
+  </si>
+  <si>
+    <t>KBLSTAGE67133-SPARES</t>
+  </si>
+  <si>
+    <t>KBLSTAGE46885</t>
+  </si>
+  <si>
+    <t>CAD699580044</t>
   </si>
 </sst>
 </file>
@@ -54,7 +81,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,12 +99,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000ff"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -109,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -128,12 +149,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -446,12 +461,12 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="32.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="25.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="23.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="26.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="25.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="23.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -570,11 +585,11 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="7">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2"/>
@@ -582,97 +597,137 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>250600000007</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
